--- a/Result/profitability/3479.xlsx
+++ b/Result/profitability/3479.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7575</v>
+        <v>1.725</v>
       </c>
       <c r="N2" t="n">
-        <v>26.08875</v>
+        <v>25.95125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6</v>
+        <v>1.55375</v>
       </c>
       <c r="N3" t="n">
-        <v>17.63125</v>
+        <v>17.39</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="N4" t="n">
-        <v>17.98375</v>
+        <v>17.62125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2825</v>
+        <v>1.345</v>
       </c>
       <c r="N5" t="n">
-        <v>18.01875</v>
+        <v>17.76875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>1.24125</v>
+        <v>1.21375</v>
       </c>
       <c r="N6" t="n">
-        <v>18.0125</v>
+        <v>17.8025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06125</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>17.79375</v>
+        <v>17.775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.91625</v>
+        <v>0.8537499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.4</v>
+        <v>16.89625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8187499999999999</v>
+        <v>0.81875</v>
       </c>
       <c r="N11" t="n">
         <v>25.1375</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2431</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1845</v>
+      </c>
+      <c r="E74" t="n">
+        <v>586</v>
+      </c>
+      <c r="F74" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="G74" t="n">
+        <v>180</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>19</v>
+      </c>
+      <c r="J74" t="n">
+        <v>199</v>
+      </c>
+      <c r="K74" t="n">
+        <v>124</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.8075</v>
+      </c>
+      <c r="N74" t="n">
+        <v>25.84375</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.5000000000000002</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.2252252252252253</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-4.029999999999998</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.1431616341030194</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.4098360655737705</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-0.07656967840735074</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
